--- a/output/quickfixopen_portfolio_daily.xlsx
+++ b/output/quickfixopen_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$182</f>
+              <f>'equity_curve'!$A$2:$A$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$182</f>
+              <f>'equity_curve'!$B$2:$B$184</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>416,960.79</t>
+          <t>422,997.97</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+316.96%</t>
+          <t>+323.00%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>427,550  (+327.55%)</t>
+          <t>434,017  (+334.02%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,514  (10.6 pts of return)</t>
+          <t>5,784  (11.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>75.4x</t>
+          <t>76.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.9%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+1.98R  (best +8.92R)</t>
+          <t>+1.97R  (best +8.92R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4,159  (+1.98%)</t>
+          <t>4,185  (+1.97%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>41% of trading days</t>
+          <t>42% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-27</t>
+          <t>2025-12-18 -&gt; 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5394,6 +5394,62 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>416960.79</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>4169.61</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>412791.18</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures short (risk 4,170)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>422997.97</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>422997.97</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 4,128)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures exit_open (+6,202)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5406,7 +5462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10081,6 +10137,100 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.512</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.488</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>706337.47</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>9818.09</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>14604.41</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>720554.62</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>696519.38</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>9681.620000000001</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>-387.26</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>705950.21</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
